--- a/results/test/vicon_shoulder_width_by_csv.xlsx
+++ b/results/test/vicon_shoulder_width_by_csv.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>csv</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>P1_shoulder_width_median_mm</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>P1_shoulder_width_mean_mm</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>P1_n_frames_used</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>P2_shoulder_width_median_mm</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P2_shoulder_width_mean_mm</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>P2_n_frames_used</t>
         </is>

--- a/results/test/vicon_shoulder_width_by_csv.xlsx
+++ b/results/test/vicon_shoulder_width_by_csv.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,28 +491,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/SEMID01.csv</t>
+          <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/SEATEDD08.csv</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SEMID01.csv</t>
+          <t>SEATEDD08.csv</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>284.5477680640457</v>
+        <v>327.8591878040019</v>
       </c>
       <c r="D3" t="n">
-        <v>283.576015586135</v>
+        <v>328.7894498690712</v>
       </c>
       <c r="E3" t="n">
         <v>18000</v>
       </c>
       <c r="F3" t="n">
-        <v>336.0979522274564</v>
+        <v>442.0891707732675</v>
       </c>
       <c r="G3" t="n">
-        <v>335.2617840300542</v>
+        <v>440.6442108333428</v>
       </c>
       <c r="H3" t="n">
         <v>18000</v>
@@ -521,30 +521,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/STANDINGD01.csv</t>
+          <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/SEMID01.csv</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STANDINGD01.csv</t>
+          <t>SEMID01.csv</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>290.3214874392707</v>
+        <v>284.5477680640457</v>
       </c>
       <c r="D4" t="n">
-        <v>288.1406817161009</v>
+        <v>283.576015586135</v>
       </c>
       <c r="E4" t="n">
         <v>18000</v>
       </c>
       <c r="F4" t="n">
+        <v>336.0979522274564</v>
+      </c>
+      <c r="G4" t="n">
+        <v>335.2617840300542</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/STANDINGD01.csv</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>STANDINGD01.csv</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>290.3214874392707</v>
+      </c>
+      <c r="D5" t="n">
+        <v>288.1406817161009</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F5" t="n">
         <v>345.8507837970011</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>345.6750574190094</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>18000</v>
       </c>
     </row>
